--- a/catalogo_productos.xlsx
+++ b/catalogo_productos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1083,26 +1083,26 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mini Sol Eterno</t>
+          <t>Rosas y Claveles</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>$53.000</t>
+          <t>$170.000</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Flores Amarillas</t>
+          <t>Amor y Amistad</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Flores Eternas</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1112,27 +1112,27 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Mini ramo de 7 rosas eternas amarillas con perlas y mariposa dorada, envuelto en papel blanco con lazo dorado. Pequeño, duradero y perfecto para el 21 de septiembre.</t>
+          <t>Ramo de 24 rosas rojas con claveles rosados y eucalipto, envuelto en papel rosa con borde plateado y tarjeta para tu mensaje. Romántico, abundante y lleno de contraste.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_49.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_63.webp</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24 Rosas Amarillas</t>
+          <t>Mini Sol Eterno</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$180.000</t>
+          <t>$53.000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1152,27 +1152,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 24 rosas amarillas con eucalipto y perlas, envuelto en papel celeste con lazo dorado. Luz y buena energía para quien te alegra la vida.</t>
+          <t>Mini ramo de 7 rosas eternas amarillas con perlas y mariposa dorada, envuelto en papel blanco con lazo dorado. Pequeño, duradero y perfecto para el 21 de septiembre.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_50.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_49.webp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Docena Eterna Dorada</t>
+          <t>24 Rosas Amarillas</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$90.000</t>
+          <t>$180.000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Flores Eternas</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,27 +1192,27 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12 rosas eternas en tono amarillo dorado con perlas y mariposa, en papel blanco con lazo dorado. Un sol que no se marchita.</t>
+          <t>Ramo de 24 rosas amarillas con eucalipto y perlas, envuelto en papel celeste con lazo dorado. Luz y buena energía para quien te alegra la vida.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_51.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_50.webp</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tulipanes Amarillos</t>
+          <t>Docena Eterna Dorada</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Desde $148.000</t>
+          <t>$90.000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Tulipanes</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1232,27 +1232,27 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Ramo de tulipanes amarillos disponible desde 4 unidades, con flor nube y papel rosado. Frescura y luz para el Día de las Flores Amarillas.</t>
+          <t>12 rosas eternas en tono amarillo dorado con perlas y mariposa, en papel blanco con lazo dorado. Un sol que no se marchita.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_52.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_51.webp</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sol y Rosas</t>
+          <t>Tulipanes Amarillos</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>$318.000</t>
+          <t>Desde $148.000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Girasoles</t>
+          <t>Tulipanes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1272,27 +1272,27 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10 girasoles con 50 rosas en tonos rosa y blanco, envueltos en papel rosa con borde dorado. Un arreglo enorme para una ocasión enorme.</t>
+          <t>Ramo de tulipanes amarillos disponible desde 4 unidades, con flor nube y papel rosado. Frescura y luz para el Día de las Flores Amarillas.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_53.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_52.webp</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Docena Amarilla</t>
+          <t>Sol y Rosas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$140.000</t>
+          <t>$318.000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Girasoles</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 12 rosas amarillas rodeadas de flor nube, en papel crema con lazo dorado. Alegría en su forma más clásica.</t>
+          <t>10 girasoles con 50 rosas en tonos rosa y blanco, envueltos en papel rosa con borde dorado. Un arreglo enorme para una ocasión enorme.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_54.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_53.webp</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tres Soles</t>
+          <t>Docena Amarilla</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$130.000</t>
+          <t>$140.000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Girasoles</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1352,27 +1352,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 3 girasoles con flor nube, envuelto en papel lila con lazo dorado. Alegría pura en un tamaño ideal para sorprender.</t>
+          <t>Ramo de 12 rosas amarillas rodeadas de flor nube, en papel crema con lazo dorado. Alegría en su forma más clásica.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_55.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_54.webp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Girasol entre Rosas</t>
+          <t>Tres Soles</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$340.000</t>
+          <t>$130.000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>60 rosas en tonos amarillo y blanco con un girasol en el centro y manzanilla, en papel dorado. Un diseño de lujo para quien lo merece todo.</t>
+          <t>Ramo de 3 girasoles con flor nube, envuelto en papel lila con lazo dorado. Alegría pura en un tamaño ideal para sorprender.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_56.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_55.webp</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Girasoles y Siempreviva</t>
+          <t>Girasol entre Rosas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$95.000</t>
+          <t>$340.000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,27 +1432,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 3 girasoles con flor siempreviva en tono lila, envuelto en papel blanco. Colorido, fresco y a muy buen precio.</t>
+          <t>60 rosas en tonos amarillo y blanco con un girasol en el centro y manzanilla, en papel dorado. Un diseño de lujo para quien lo merece todo.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_57.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_56.webp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Seis Girasoles</t>
+          <t>Girasoles y Siempreviva</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$145.000</t>
+          <t>$95.000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1472,27 +1472,27 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 6 girasoles con flor nube, envuelto en papel crema con tarjeta Duquesa. Grande, radiante y listo para alegrar el día.</t>
+          <t>Ramo de 3 girasoles con flor siempreviva en tono lila, envuelto en papel blanco. Colorido, fresco y a muy buen precio.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_58.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_57.webp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Corazón Dorado</t>
+          <t>Seis Girasoles</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$103.000</t>
+          <t>$145.000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Flores Eternas</t>
+          <t>Girasoles</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1512,37 +1512,37 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Caja corazón con rosas eternas amarillas, mariposa dorada y 12 Ferrero Rocher, con lazo amarillo. Un detalle que dura y endulza.</t>
+          <t>Ramo de 6 girasoles con flor nube, envuelto en papel crema con tarjeta Duquesa. Grande, radiante y listo para alegrar el día.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_61.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_58.webp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ternura Kitty</t>
+          <t>Corazón Dorado</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$520.000</t>
+          <t>$103.000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Más Arreglos</t>
+          <t>Flores Amarillas</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Especiales</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1552,37 +1552,37 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Arreglo escultórico en forma de Hello Kitty con crisantemos blancos, moño de rosas rosadas y detalles en rosas amarillas. Una pieza única para sorprender de verdad.</t>
+          <t>Caja corazón con rosas eternas amarillas, mariposa dorada y 12 Ferrero Rocher, con lazo amarillo. Un detalle que dura y endulza.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_27.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_61.webp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Jardín Encantado</t>
+          <t>Girasoles Rosé</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$545.000</t>
+          <t>$90.000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Más Arreglos</t>
+          <t>Flores Amarillas</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Especiales</t>
+          <t>Girasoles</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Caja rosa con orquídeas cymbidium, lirios naranjas, girasoles, gerberas y rosas lavanda entre hortensias y claveles. Color y sofisticación en gran formato.</t>
+          <t>Ramo de 3 girasoles con claveles rosados, rosas durazno, flor nube y eucalipto, envuelto en papel rosa con lazo. Alegría y ternura en un solo detalle.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_32.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_62.webp</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Noche Estrellada</t>
+          <t>Ternura Kitty</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$160.000</t>
+          <t>$520.000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1632,37 +1632,37 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Ramo inspirado en “La Noche Estrellada” de Van Gogh: hortensias y rosas azules con crisantemos amarillos y lámina de la obra. Arte que florece.</t>
+          <t>Arreglo escultórico en forma de Hello Kitty con crisantemos blancos, moño de rosas rosadas y detalles en rosas amarillas. Una pieza única para sorprender de verdad.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_35.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_27.webp</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amor de 200 Rosas</t>
+          <t>Jardín Encantado</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$820.000</t>
+          <t>$545.000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Amor y Amistad</t>
+          <t>Más Arreglos</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Especiales</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1672,27 +1672,27 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>200 rosas rojas coronadas con iniciales personalizadas en flor nube, envueltas en papel negro. El gesto más grande que puedes regalar.</t>
+          <t>Caja rosa con orquídeas cymbidium, lirios naranjas, girasoles, gerberas y rosas lavanda entre hortensias y claveles. Color y sofisticación en gran formato.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_28.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_32.webp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Fuego Silvestre</t>
+          <t>Noche Estrellada</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$360.000</t>
+          <t>$160.000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1702,7 +1702,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Especiales</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1712,32 +1712,32 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Ramo rojo con rosas, gerberas, claveles y astromelias, envuelto en papel blanco. Intensidad y elegancia para una ocasión inolvidable.</t>
+          <t>Ramo inspirado en “La Noche Estrellada” de Van Gogh: hortensias y rosas azules con crisantemos amarillos y lámina de la obra. Arte que florece.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_29.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_35.webp</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Corazón Ferrero</t>
+          <t>Amor de 200 Rosas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$650.000</t>
+          <t>$820.000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Más Arreglos</t>
+          <t>Amor y Amistad</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1752,27 +1752,27 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Corazón con 33 Ferrero Rocher al centro, 52 rosas rojas y billetes decorativos a elección. Precio base del ramo; el dinero se ajusta a tu gusto.</t>
+          <t>200 rosas rojas coronadas con iniciales personalizadas en flor nube, envueltas en papel negro. El gesto más grande que puedes regalar.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_30.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_28.webp</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ruta de Campeón</t>
+          <t>Fuego Silvestre</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>$167.000</t>
+          <t>$360.000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>12 rosas rojas con flor nube y 5 carritos Hot Wheels. El regalo perfecto para los amantes de los autos.</t>
+          <t>Ramo rojo con rosas, gerberas, claveles y astromelias, envuelto en papel blanco. Intensidad y elegancia para una ocasión inolvidable.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_31.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_29.webp</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cerezo Rojo</t>
+          <t>Corazón Ferrero</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>$265.000</t>
+          <t>$650.000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1832,907 +1832,887 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>60 rosas rojas con cerezas y moño rosado, envueltas en tul beige. Pasión y dulzura en una sola presentación.</t>
+          <t>Corazón con 33 Ferrero Rocher al centro, 52 rosas rojas y billetes decorativos a elección. Precio base del ramo; el dinero se ajusta a tu gusto.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_33.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_30.webp</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ruta de Campeón</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>$167.000</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Más Arreglos</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Rosas</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>12 rosas rojas con flor nube y 5 carritos Hot Wheels. El regalo perfecto para los amantes de los autos.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_31.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Cerezo Rojo</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>$265.000</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Más Arreglos</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Rosas</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>60 rosas rojas con cerezas y moño rosado, envueltas en tul beige. Pasión y dulzura en una sola presentación.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_33.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
         <v>34</v>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Nube Pastel</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>$232.000</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D38" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>36 rosas con mini rosas y claveles en tonos rosa, amarillo y pastel, en papel lila. Ternura y frescura en cada pétalo.</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_34.webp</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
+    <row r="39">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Despertar de Primavera</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Desde $148.000</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Tulipanes</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Bouquet de tulipanes en 4, 6 o 10 unidades, de un solo color o combinados. Elegante y versátil para cualquier ocasión.</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/ofertas/imagenes/tulipanes/tulipanes_amarillos.webp</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
+    <row r="40">
+      <c r="B40" t="inlineStr">
         <is>
           <t>Cápsula de Eternidad</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>$53.000</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D40" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Flores Eternas</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>Mini ramo de 7 rosas eternas con perlas y mariposas decorativas. Disponible en varios colores.</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/mini_ramo_eternas.webp</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
+    <row r="41">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Legado Inmortal</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>$145.000</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Flores Eternas</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>Bouquet de 20 rosas eternas con malla de perlas y mariposas doradas. Incluye listón y mensaje personalizado.</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/bouquet_eternas.webp</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
+    <row r="42">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Imperio Eterno</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>$220.000</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>Flores Eternas</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>Bouquet de 34 rosas eternas con perlas y mariposas. Incluye moño y mensaje especial.</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/bouquet_eternas_grandes.webp</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
+    <row r="43">
+      <c r="B43" t="inlineStr">
         <is>
           <t>Celebración de Vida</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>$140.000</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D43" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>Bouquet de 20 rosas frescas con eucalipto en base que las mantiene radiantes. Incluye tarjeta personalizada.</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramo_flores_cumpleanos.webp</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
+    <row r="44">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Juramento Sagrado</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>$155.000</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>Bouquet de 18 rosas frescas con follajes y listón decorativo. Diseño delicado para el día más especial.</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramos_novias_naturales.webp</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
+    <row r="45">
+      <c r="B45" t="inlineStr">
         <is>
           <t>Coronación de Princesa</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>$255.000</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>48 rosas frescas rodeadas de flor nube, con corona dorada y listón con mensaje. Perfecto para los 15 años.</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramo_flores_quinceaneras.webp</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr">
+    <row r="46">
+      <c r="B46" t="inlineStr">
         <is>
           <t>Arsenal Completo</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>$177.500</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D46" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>Rosas frescas, flor nube y 11 Ferrero Rocher en base elegante con lazo dorado. El detalle que cubre todas las expectativas.</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/amoryamistad/amoryamistad2.webp</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
+    <row r="47">
+      <c r="B47" t="inlineStr">
         <is>
           <t>Alegría Multicolor</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>$60.000</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Cumpleaños</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>Bouquet de astromelias frescas con base de oasis y tarjeta personalizada. Color y frescura que duran varios días.</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos5.webp</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
+    <row r="48">
+      <c r="B48" t="inlineStr">
         <is>
           <t>Monumento de Amor</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>$465.000</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D48" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>110 rosas en forma de corazón con mensaje en listón y 2 globos de helio. Una declaración imposible de olvidar.</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos1.webp</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
+    <row r="49">
+      <c r="B49" t="inlineStr">
         <is>
           <t>Estrella Resplandeciente</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C49" t="inlineStr">
         <is>
           <t>$60.000</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D49" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Cumpleaños</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>Bouquet de claveles de larga duración con tarjeta personalizada. Ideal para celebrar años de amistad.</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos6.webp</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
+    <row r="50">
+      <c r="B50" t="inlineStr">
         <is>
           <t>Sinfonía Dorada</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>$280.000</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>56 rosas con un girasol radiante y manzanilla. Elegancia y felicidad en un solo ramo.</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos2.webp</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
+    <row r="51">
+      <c r="B51" t="inlineStr">
         <is>
           <t>Nube de Celebración</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>$255.000</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>52 rosas frescas con flor nube y moño decorativo. Sofisticación pura para celebrar con estilo.</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos3.webp</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
+    <row r="52">
+      <c r="B52" t="inlineStr">
         <is>
           <t>Esencia de Felicidad</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>$160.000</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>20 rosas frescas en arreglo clásico con tarjeta personalizada. Afecto directo al corazón, sin complicaciones.</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos4.webp</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
+    <row r="53">
+      <c r="B53" t="inlineStr">
         <is>
           <t>Just For You</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>$89.000</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Detalles</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>Caja con rosas artificiales de alta calidad y un globo con mensaje especial. Un detalle que dura meses impecable.</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores25.webp</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
+    <row r="54">
+      <c r="B54" t="inlineStr">
         <is>
           <t>Detalle Natural</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>$86.000</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Detalles</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Flores naturales acompañadas de dos Ferrero Rocher. Frescura, color y dulzura en un solo regalo.</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores27.webp</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
+    <row r="55">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Eternidad Floral</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>$110.000</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Detalles</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Detalle de flores artificiales de alta calidad y larga duración. Un recuerdo elegante para conservar.</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores28.webp</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
+    <row r="56">
+      <c r="B56" t="inlineStr">
         <is>
           <t>Sol Radiante</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C56" t="inlineStr">
         <is>
           <t>$480.000</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D56" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Girasoles</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>Caja blanca con girasoles, rosas amarillas, crisantemos, claveles y eucalipto. Una declaración de cariño en gran formato.</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores29.webp</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
+    <row r="57">
+      <c r="B57" t="inlineStr">
         <is>
           <t>Elegancia Rosada</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C57" t="inlineStr">
         <is>
           <t>$200.000</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D57" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Cajas</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>Caja redonda rosa con hortensias, rosas y crisantemos en tonos pastel. Romántico, femenino y elegante.</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores33.webp</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr">
+    <row r="58">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Reina del Sol</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C58" t="inlineStr">
         <is>
           <t>$450.000</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Girasoles</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>Bouquet con varios girasoles y rosas rojas, papel decorativo y listón blanco con inscripción dorada. Un homenaje monumental.</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores38.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>25</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Romance Duquesa</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>$165.000</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>OCULTO (foto 1–26)</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>Rosas</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>No (oculto temporalmente)</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>Bolsa Duquesa Floral “Flower World” en dos versiones: rosas rojas con claveles e hipérico, o rosas rosadas con lisianthus. Presentación premium con paniculata y eucalipto.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_25.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>18</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Despertar de Alegría</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>$95.000</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>OCULTO (foto 1–26)</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Gerberas</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>No (oculto temporalmente)</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>Ramo de 10 gerberas con tarjeta o mensaje personalizado. Color y alegría al instante.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_18.webp</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fusión Perfecta</t>
+          <t>Romance Duquesa</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>$227.500</t>
+          <t>$165.000</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2752,27 +2732,27 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 36 rosas y 6 girasoles con tarjeta personalizada. Elegancia y energía en un solo ramo.</t>
+          <t>Bolsa Duquesa Floral “Flower World” en dos versiones: rosas rojas con claveles e hipérico, o rosas rosadas con lisianthus. Presentación premium con paniculata y eucalipto.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_2.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_25.webp</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Garantía de Amor</t>
+          <t>Despertar de Alegría</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>$102.500</t>
+          <t>$95.000</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2782,7 +2762,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Gerberas</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2792,27 +2772,27 @@
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 12 rosas con tarjeta o mensaje personalizado. El clásico que siempre funciona.</t>
+          <t>Ramo de 10 gerberas con tarjeta o mensaje personalizado. Color y alegría al instante.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_17.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_18.webp</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Conquista Definitiva</t>
+          <t>Fusión Perfecta</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>$165.000</t>
+          <t>$227.500</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2832,27 +2812,27 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 24 rosas y claveles con tarjeta personalizada. Para dejar claro lo que sientes.</t>
+          <t>Ramo de 36 rosas y 6 girasoles con tarjeta personalizada. Elegancia y energía en un solo ramo.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_21.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_2.webp</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Obra Maestra</t>
+          <t>Garantía de Amor</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>$265.000</t>
+          <t>$102.500</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2872,27 +2852,27 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 60 rosas y claveles con tarjeta personalizada. Abundancia que impresiona.</t>
+          <t>Ramo de 12 rosas con tarjeta o mensaje personalizado. El clásico que siempre funciona.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_1.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_17.webp</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vitamina Emocional</t>
+          <t>Conquista Definitiva</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>$110.000</t>
+          <t>$165.000</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2902,7 +2882,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Girasoles</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2912,27 +2892,27 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 4 girasoles con tarjeta o mensaje personalizado. Alegría garantizada.</t>
+          <t>Ramo de 24 rosas y claveles con tarjeta personalizada. Para dejar claro lo que sientes.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_23.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_21.webp</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Guardián del Corazón</t>
+          <t>Obra Maestra</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>$275.000</t>
+          <t>$265.000</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2942,7 +2922,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Con Peluche</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2952,50 +2932,130 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Osito de 25 cm en rosas de foamy dentro de caja de acetato, con tarjeta y 3 globos de helio. Un detalle que perdura.</t>
+          <t>Ramo de 60 rosas y claveles con tarjeta personalizada. Abundancia que impresiona.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_24.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_1.webp</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
+        <v>23</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Vitamina Emocional</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>$110.000</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OCULTO (foto 1–26)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Girasoles</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>No (oculto temporalmente)</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>Ramo de 4 girasoles con tarjeta o mensaje personalizado. Alegría garantizada.</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_23.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>24</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Guardián del Corazón</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>$275.000</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OCULTO (foto 1–26)</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Con Peluche</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>No (oculto temporalmente)</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>Osito de 25 cm en rosas de foamy dentro de caja de acetato, con tarjeta y 3 globos de helio. Un detalle que perdura.</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_24.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
         <v>26</v>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B67" t="inlineStr">
         <is>
           <t>Reflejo de Amor</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>$212.000</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D67" t="inlineStr">
         <is>
           <t>OCULTO (foto 1–26)</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>No (oculto temporalmente)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>Arreglo circular de rosas rojas alrededor de un espejo grabado “Eres la mejor mamá”. Elegancia con un mensaje eterno.</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_26.webp</t>
         </is>

--- a/catalogo_productos.xlsx
+++ b/catalogo_productos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H67"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1123,26 +1123,26 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Mini Sol Eterno</t>
+          <t>Dulce Despertar</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$53.000</t>
+          <t>$147.000</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Flores Amarillas</t>
+          <t>Amor y Amistad</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Flores Eternas</t>
+          <t>Desayunos</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1152,37 +1152,37 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Mini ramo de 7 rosas eternas amarillas con perlas y mariposa dorada, envuelto en papel blanco con lazo dorado. Pequeño, duradero y perfecto para el 21 de septiembre.</t>
+          <t>Una deliciosa bandeja que combina lo dulce y lo salado: suaves wafles con frutas frescas, sándwich de jamón, queso y lechuga, jugo natural de naranja y chocolisto cremoso. Acompañan copa de yogur griego con frutas y granola, mix de uvas, brownie, jamón, queso y un Ferrero Rocher.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_49.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_64.webp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24 Rosas Amarillas</t>
+          <t>Romance en Bandeja</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>$180.000</t>
+          <t>$265.000</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Flores Amarillas</t>
+          <t>Amor y Amistad</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Desayunos</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1192,37 +1192,37 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 24 rosas amarillas con eucalipto y perlas, envuelto en papel celeste con lazo dorado. Luz y buena energía para quien te alegra la vida.</t>
+          <t>Bandeja premium con ensalada de frutas con crema de leche, wraps de pollo, jamón, queso y lechuga, mini arepas con queso o salchicha, bebida a elección (café o chocolisto), soda Hatsu y postre casero. Incluye hermoso jarrón de rosas rojas y globo personalizado.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_50.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_65.webp</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Docena Eterna Dorada</t>
+          <t>Experiencia Dulce</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>$90.000</t>
+          <t>$180.000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Flores Amarillas</t>
+          <t>Amor y Amistad</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Flores Eternas</t>
+          <t>Desayunos</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1232,27 +1232,27 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12 rosas eternas en tono amarillo dorado con perlas y mariposa, en papel blanco con lazo dorado. Un sol que no se marchita.</t>
+          <t>Bandeja deliciosa y equilibrada con suaves wafles cubiertos de frutas frescas, wraps de pollo, jamón, queso y lechuga, copa de yogur griego con frutas y granola, brownie con frutos secos, jugo natural de naranja y chocolisto cremoso.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_51.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_66.webp</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tulipanes Amarillos</t>
+          <t>Mini Sol Eterno</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Desde $148.000</t>
+          <t>$53.000</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1262,7 +1262,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tulipanes</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1272,27 +1272,27 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Ramo de tulipanes amarillos disponible desde 4 unidades, con flor nube y papel rosado. Frescura y luz para el Día de las Flores Amarillas.</t>
+          <t>Mini ramo de 7 rosas eternas amarillas con perlas y mariposa dorada, envuelto en papel blanco con lazo dorado. Pequeño, duradero y perfecto para el 21 de septiembre.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_52.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_49.webp</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sol y Rosas</t>
+          <t>24 Rosas Amarillas</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>$318.000</t>
+          <t>$180.000</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Girasoles</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1312,27 +1312,27 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10 girasoles con 50 rosas en tonos rosa y blanco, envueltos en papel rosa con borde dorado. Un arreglo enorme para una ocasión enorme.</t>
+          <t>Ramo de 24 rosas amarillas con eucalipto y perlas, envuelto en papel celeste con lazo dorado. Luz y buena energía para quien te alegra la vida.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_53.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_50.webp</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Docena Amarilla</t>
+          <t>Docena Eterna Dorada</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>$140.000</t>
+          <t>$90.000</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1352,27 +1352,27 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 12 rosas amarillas rodeadas de flor nube, en papel crema con lazo dorado. Alegría en su forma más clásica.</t>
+          <t>12 rosas eternas en tono amarillo dorado con perlas y mariposa, en papel blanco con lazo dorado. Un sol que no se marchita.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_54.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_51.webp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tres Soles</t>
+          <t>Tulipanes Amarillos</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>$130.000</t>
+          <t>Desde $148.000</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Girasoles</t>
+          <t>Tulipanes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1392,27 +1392,27 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 3 girasoles con flor nube, envuelto en papel lila con lazo dorado. Alegría pura en un tamaño ideal para sorprender.</t>
+          <t>Ramo de tulipanes amarillos disponible desde 4 unidades, con flor nube y papel rosado. Frescura y luz para el Día de las Flores Amarillas.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_55.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_52.webp</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Girasol entre Rosas</t>
+          <t>Sol y Rosas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>$340.000</t>
+          <t>$318.000</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1432,27 +1432,27 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>60 rosas en tonos amarillo y blanco con un girasol en el centro y manzanilla, en papel dorado. Un diseño de lujo para quien lo merece todo.</t>
+          <t>10 girasoles con 50 rosas en tonos rosa y blanco, envueltos en papel rosa con borde dorado. Un arreglo enorme para una ocasión enorme.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_56.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_53.webp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Girasoles y Siempreviva</t>
+          <t>Docena Amarilla</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>$95.000</t>
+          <t>$140.000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Girasoles</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1472,27 +1472,27 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 3 girasoles con flor siempreviva en tono lila, envuelto en papel blanco. Colorido, fresco y a muy buen precio.</t>
+          <t>Ramo de 12 rosas amarillas rodeadas de flor nube, en papel crema con lazo dorado. Alegría en su forma más clásica.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_57.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_54.webp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Seis Girasoles</t>
+          <t>Tres Soles</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>$145.000</t>
+          <t>$130.000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1512,27 +1512,27 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 6 girasoles con flor nube, envuelto en papel crema con tarjeta Duquesa. Grande, radiante y listo para alegrar el día.</t>
+          <t>Ramo de 3 girasoles con flor nube, envuelto en papel lila con lazo dorado. Alegría pura en un tamaño ideal para sorprender.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_58.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_55.webp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Corazón Dorado</t>
+          <t>Girasol entre Rosas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>$103.000</t>
+          <t>$340.000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flores Eternas</t>
+          <t>Girasoles</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1552,27 +1552,27 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Caja corazón con rosas eternas amarillas, mariposa dorada y 12 Ferrero Rocher, con lazo amarillo. Un detalle que dura y endulza.</t>
+          <t>60 rosas en tonos amarillo y blanco con un girasol en el centro y manzanilla, en papel dorado. Un diseño de lujo para quien lo merece todo.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_61.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_56.webp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Girasoles Rosé</t>
+          <t>Girasoles y Siempreviva</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>$90.000</t>
+          <t>$95.000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1592,37 +1592,37 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 3 girasoles con claveles rosados, rosas durazno, flor nube y eucalipto, envuelto en papel rosa con lazo. Alegría y ternura en un solo detalle.</t>
+          <t>Ramo de 3 girasoles con flor siempreviva en tono lila, envuelto en papel blanco. Colorido, fresco y a muy buen precio.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_62.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_57.webp</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ternura Kitty</t>
+          <t>Seis Girasoles</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>$520.000</t>
+          <t>$145.000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Más Arreglos</t>
+          <t>Flores Amarillas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Especiales</t>
+          <t>Girasoles</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1632,37 +1632,37 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Arreglo escultórico en forma de Hello Kitty con crisantemos blancos, moño de rosas rosadas y detalles en rosas amarillas. Una pieza única para sorprender de verdad.</t>
+          <t>Ramo de 6 girasoles con flor nube, envuelto en papel crema con tarjeta Duquesa. Grande, radiante y listo para alegrar el día.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_27.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_58.webp</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Jardín Encantado</t>
+          <t>Corazón Dorado</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>$545.000</t>
+          <t>$103.000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Más Arreglos</t>
+          <t>Flores Amarillas</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Especiales</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1672,37 +1672,37 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Caja rosa con orquídeas cymbidium, lirios naranjas, girasoles, gerberas y rosas lavanda entre hortensias y claveles. Color y sofisticación en gran formato.</t>
+          <t>Caja corazón con rosas eternas amarillas, mariposa dorada y 9 Ferrero Rocher, con lazo amarillo. Un detalle que dura y endulza.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_32.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_61.webp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Noche Estrellada</t>
+          <t>Girasoles Rosé</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>$160.000</t>
+          <t>$90.000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Más Arreglos</t>
+          <t>Flores Amarillas</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Especiales</t>
+          <t>Girasoles</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1712,37 +1712,37 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Ramo inspirado en “La Noche Estrellada” de Van Gogh: hortensias y rosas azules con crisantemos amarillos y lámina de la obra. Arte que florece.</t>
+          <t>Ramo de 3 girasoles con claveles rosados, rosas durazno, flor nube y eucalipto, envuelto en papel rosa con lazo. Alegría y ternura en un solo detalle.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_35.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_62.webp</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amor de 200 Rosas</t>
+          <t>Ternura Kitty</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>$820.000</t>
+          <t>$520.000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Amor y Amistad</t>
+          <t>Más Arreglos</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Especiales</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1752,27 +1752,27 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>200 rosas rojas coronadas con iniciales personalizadas en flor nube, envueltas en papel negro. El gesto más grande que puedes regalar.</t>
+          <t>Arreglo escultórico en forma de Hello Kitty con crisantemos blancos, moño de rosas rosadas y detalles en rosas amarillas. Una pieza única para sorprender de verdad.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_28.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_27.webp</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fuego Silvestre</t>
+          <t>Jardín Encantado</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>$360.000</t>
+          <t>$545.000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Especiales</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1792,27 +1792,27 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Ramo rojo con rosas, gerberas, claveles y astromelias, envuelto en papel blanco. Intensidad y elegancia para una ocasión inolvidable.</t>
+          <t>Caja rosa con orquídeas cymbidium, lirios naranjas, girasoles, gerberas y rosas lavanda entre hortensias y claveles. Color y sofisticación en gran formato.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_29.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_32.webp</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Corazón Ferrero</t>
+          <t>Noche Estrellada</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>$650.000</t>
+          <t>$160.000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Especiales</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1832,32 +1832,32 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Corazón con 33 Ferrero Rocher al centro, 52 rosas rojas y billetes decorativos a elección. Precio base del ramo; el dinero se ajusta a tu gusto.</t>
+          <t>Ramo inspirado en “La Noche Estrellada” de Van Gogh: hortensias y rosas azules con crisantemos amarillos y lámina de la obra. Arte que florece.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_30.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_35.webp</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ruta de Campeón</t>
+          <t>Amor de 200 Rosas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>$167.000</t>
+          <t>$820.000</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Más Arreglos</t>
+          <t>Amor y Amistad</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1872,27 +1872,27 @@
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>12 rosas rojas con flor nube y 5 carritos Hot Wheels. El regalo perfecto para los amantes de los autos.</t>
+          <t>200 rosas rojas coronadas con iniciales personalizadas en flor nube, envueltas en papel negro. El gesto más grande que puedes regalar.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_31.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_28.webp</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cerezo Rojo</t>
+          <t>Fuego Silvestre</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>$265.000</t>
+          <t>$360.000</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1912,175 +1912,184 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>60 rosas rojas con cerezas y moño rosado, envueltas en tul beige. Pasión y dulzura en una sola presentación.</t>
+          <t>Ramo rojo con rosas, gerberas, claveles y astromelias, envuelto en papel blanco. Intensidad y elegancia para una ocasión inolvidable.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_33.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_29.webp</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
+        <v>30</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Corazón Ferrero</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>$650.000</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Más Arreglos</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Rosas</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Corazón con 33 Ferrero Rocher al centro, 52 rosas rojas y billetes decorativos a elección. Precio base del ramo; el dinero se ajusta a tu gusto.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_30.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>31</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Ruta de Campeón</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>$167.000</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Más Arreglos</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Rosas</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>12 rosas rojas con flor nube y 5 carritos Hot Wheels. El regalo perfecto para los amantes de los autos.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_31.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Cerezo Rojo</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>$265.000</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Más Arreglos</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Rosas</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>60 rosas rojas con cerezas y moño rosado, envueltas en tul beige. Pasión y dulzura en una sola presentación.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_33.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>34</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Nube Pastel</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>$232.000</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>36 rosas con mini rosas y claveles en tonos rosa, amarillo y pastel, en papel lila. Ternura y frescura en cada pétalo.</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_34.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Despertar de Primavera</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Desde $148.000</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Más Arreglos</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Tulipanes</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Bouquet de tulipanes en 4, 6 o 10 unidades, de un solo color o combinados. Elegante y versátil para cualquier ocasión.</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>https://florescucuta.dondeseria.com/ofertas/imagenes/tulipanes/tulipanes_amarillos.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Cápsula de Eternidad</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>$53.000</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Más Arreglos</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Flores Eternas</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Mini ramo de 7 rosas eternas con perlas y mariposas decorativas. Disponible en varios colores.</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>https://florescucuta.dondeseria.com/assets/mini_ramo_eternas.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Legado Inmortal</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>$145.000</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Más Arreglos</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Flores Eternas</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Bouquet de 20 rosas eternas con malla de perlas y mariposas doradas. Incluye listón y mensaje personalizado.</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>https://florescucuta.dondeseria.com/assets/bouquet_eternas.webp</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>Imperio Eterno</t>
+          <t>Despertar de Primavera</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>$220.000</t>
+          <t>Desde $148.000</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2090,7 +2099,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Flores Eternas</t>
+          <t>Tulipanes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2100,24 +2109,24 @@
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Bouquet de 34 rosas eternas con perlas y mariposas. Incluye moño y mensaje especial.</t>
+          <t>Bouquet de tulipanes en 4, 6 o 10 unidades, de un solo color o combinados. Elegante y versátil para cualquier ocasión.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/bouquet_eternas_grandes.webp</t>
+          <t>https://florescucuta.dondeseria.com/ofertas/imagenes/tulipanes/tulipanes_amarillos.webp</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>Celebración de Vida</t>
+          <t>Cápsula de Eternidad</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>$140.000</t>
+          <t>$53.000</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2127,7 +2136,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2137,24 +2146,24 @@
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>Bouquet de 20 rosas frescas con eucalipto en base que las mantiene radiantes. Incluye tarjeta personalizada.</t>
+          <t>Mini ramo de 7 rosas eternas con perlas y mariposas decorativas. Disponible en varios colores.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramo_flores_cumpleanos.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/mini_ramo_eternas.webp</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>Juramento Sagrado</t>
+          <t>Legado Inmortal</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>$155.000</t>
+          <t>$145.000</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2164,7 +2173,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2174,24 +2183,24 @@
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>Bouquet de 18 rosas frescas con follajes y listón decorativo. Diseño delicado para el día más especial.</t>
+          <t>Bouquet de 20 rosas eternas con malla de perlas y mariposas doradas. Incluye listón y mensaje personalizado.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramos_novias_naturales.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/bouquet_eternas.webp</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>Coronación de Princesa</t>
+          <t>Imperio Eterno</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>$255.000</t>
+          <t>$220.000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2201,7 +2210,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Flores Eternas</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2211,24 +2220,24 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>48 rosas frescas rodeadas de flor nube, con corona dorada y listón con mensaje. Perfecto para los 15 años.</t>
+          <t>Bouquet de 34 rosas eternas con perlas y mariposas. Incluye moño y mensaje especial.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramo_flores_quinceaneras.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/bouquet_eternas_grandes.webp</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>Arsenal Completo</t>
+          <t>Celebración de Vida</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>$177.500</t>
+          <t>$140.000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2248,24 +2257,24 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Rosas frescas, flor nube y 11 Ferrero Rocher en base elegante con lazo dorado. El detalle que cubre todas las expectativas.</t>
+          <t>Bouquet de 20 rosas frescas con eucalipto en base que las mantiene radiantes. Incluye tarjeta personalizada.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/amoryamistad/amoryamistad2.webp</t>
+          <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramo_flores_cumpleanos.webp</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>Alegría Multicolor</t>
+          <t>Juramento Sagrado</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>$60.000</t>
+          <t>$155.000</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2275,7 +2284,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cumpleaños</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2285,24 +2294,24 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>Bouquet de astromelias frescas con base de oasis y tarjeta personalizada. Color y frescura que duran varios días.</t>
+          <t>Bouquet de 18 rosas frescas con follajes y listón decorativo. Diseño delicado para el día más especial.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos5.webp</t>
+          <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramos_novias_naturales.webp</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>Monumento de Amor</t>
+          <t>Coronación de Princesa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>$465.000</t>
+          <t>$255.000</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2322,24 +2331,24 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>110 rosas en forma de corazón con mensaje en listón y 2 globos de helio. Una declaración imposible de olvidar.</t>
+          <t>48 rosas frescas rodeadas de flor nube, con corona dorada y listón con mensaje. Perfecto para los 15 años.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos1.webp</t>
+          <t>https://florescucuta.dondeseria.com/ofertas/imagenes/ramo_bouquets/ramo_flores_quinceaneras.webp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>Estrella Resplandeciente</t>
+          <t>Arsenal Completo</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>$60.000</t>
+          <t>$177.500</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2349,7 +2358,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cumpleaños</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2359,24 +2368,24 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>Bouquet de claveles de larga duración con tarjeta personalizada. Ideal para celebrar años de amistad.</t>
+          <t>Rosas frescas, flor nube y 11 Ferrero Rocher en base elegante con lazo dorado. El detalle que cubre todas las expectativas.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos6.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/amoryamistad/amoryamistad2.webp</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sinfonía Dorada</t>
+          <t>Alegría Multicolor</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>$280.000</t>
+          <t>$60.000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2386,7 +2395,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Cumpleaños</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2396,24 +2405,24 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>56 rosas con un girasol radiante y manzanilla. Elegancia y felicidad en un solo ramo.</t>
+          <t>Bouquet de astromelias frescas con base de oasis y tarjeta personalizada. Color y frescura que duran varios días.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos2.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos5.webp</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nube de Celebración</t>
+          <t>Monumento de Amor</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>$255.000</t>
+          <t>$465.000</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2433,24 +2442,24 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>52 rosas frescas con flor nube y moño decorativo. Sofisticación pura para celebrar con estilo.</t>
+          <t>110 rosas en forma de corazón con mensaje en listón y 2 globos de helio. Una declaración imposible de olvidar.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos3.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos1.webp</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>Esencia de Felicidad</t>
+          <t>Estrella Resplandeciente</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>$160.000</t>
+          <t>$60.000</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2460,7 +2469,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Cumpleaños</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2470,24 +2479,24 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>20 rosas frescas en arreglo clásico con tarjeta personalizada. Afecto directo al corazón, sin complicaciones.</t>
+          <t>Bouquet de claveles de larga duración con tarjeta personalizada. Ideal para celebrar años de amistad.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos4.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos6.webp</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>Just For You</t>
+          <t>Sinfonía Dorada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>$89.000</t>
+          <t>$280.000</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2497,7 +2506,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Detalles</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2507,24 +2516,24 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>Caja con rosas artificiales de alta calidad y un globo con mensaje especial. Un detalle que dura meses impecable.</t>
+          <t>56 rosas con un girasol radiante y manzanilla. Elegancia y felicidad en un solo ramo.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores25.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos2.webp</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>Detalle Natural</t>
+          <t>Nube de Celebración</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>$86.000</t>
+          <t>$255.000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2534,7 +2543,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Detalles</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2544,24 +2553,24 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Flores naturales acompañadas de dos Ferrero Rocher. Frescura, color y dulzura en un solo regalo.</t>
+          <t>52 rosas frescas con flor nube y moño decorativo. Sofisticación pura para celebrar con estilo.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores27.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos3.webp</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eternidad Floral</t>
+          <t>Esencia de Felicidad</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>$110.000</t>
+          <t>$160.000</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2571,7 +2580,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Detalles</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2581,24 +2590,24 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Detalle de flores artificiales de alta calidad y larga duración. Un recuerdo elegante para conservar.</t>
+          <t>20 rosas frescas en arreglo clásico con tarjeta personalizada. Afecto directo al corazón, sin complicaciones.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores28.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/cumpleanos/cumpleanos4.webp</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sol Radiante</t>
+          <t>Just For You</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>$480.000</t>
+          <t>$89.000</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2608,7 +2617,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Girasoles</t>
+          <t>Detalles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2618,24 +2627,24 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Caja blanca con girasoles, rosas amarillas, crisantemos, claveles y eucalipto. Una declaración de cariño en gran formato.</t>
+          <t>Caja con rosas artificiales de alta calidad y un globo con mensaje especial. Un detalle que dura meses impecable.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores29.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores25.webp</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>Elegancia Rosada</t>
+          <t>Detalle Natural</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>$200.000</t>
+          <t>$86.000</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2645,7 +2654,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cajas</t>
+          <t>Detalles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2655,184 +2664,175 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Caja redonda rosa con hortensias, rosas y crisantemos en tonos pastel. Romántico, femenino y elegante.</t>
+          <t>Flores naturales acompañadas de dos Ferrero Rocher. Frescura, color y dulzura en un solo regalo.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores33.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores27.webp</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
+          <t>Eternidad Floral</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>$110.000</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Más Arreglos</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Detalles</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>Detalle de flores artificiales de alta calidad y larga duración. Un recuerdo elegante para conservar.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores28.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Sol Radiante</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>$480.000</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Más Arreglos</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Girasoles</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>Caja blanca con girasoles, rosas amarillas, crisantemos, claveles y eucalipto. Una declaración de cariño en gran formato.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores29.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Elegancia Rosada</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>$200.000</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Más Arreglos</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Cajas</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>Caja redonda rosa con hortensias, rosas y crisantemos en tonos pastel. Romántico, femenino y elegante.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores33.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
           <t>Reina del Sol</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>$450.000</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>Más Arreglos</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Girasoles</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>Bouquet con varios girasoles y rosas rojas, papel decorativo y listón blanco con inscripción dorada. Un homenaje monumental.</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/dia_madres/flores38.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>25</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Romance Duquesa</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>$165.000</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>OCULTO (foto 1–26)</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>Rosas</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>No (oculto temporalmente)</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>Bolsa Duquesa Floral “Flower World” en dos versiones: rosas rojas con claveles e hipérico, o rosas rosadas con lisianthus. Presentación premium con paniculata y eucalipto.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_25.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>18</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Despertar de Alegría</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>$95.000</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>OCULTO (foto 1–26)</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Gerberas</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>No (oculto temporalmente)</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>Ramo de 10 gerberas con tarjeta o mensaje personalizado. Color y alegría al instante.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_18.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Fusión Perfecta</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>$227.500</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>OCULTO (foto 1–26)</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Rosas</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>No (oculto temporalmente)</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>Ramo de 36 rosas y 6 girasoles con tarjeta personalizada. Elegancia y energía en un solo ramo.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_2.webp</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Garantía de Amor</t>
+          <t>Romance Duquesa</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>$102.500</t>
+          <t>$165.000</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2852,27 +2852,27 @@
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 12 rosas con tarjeta o mensaje personalizado. El clásico que siempre funciona.</t>
+          <t>Bolsa Duquesa Floral “Flower World” en dos versiones: rosas rojas con claveles e hipérico, o rosas rosadas con lisianthus. Presentación premium con paniculata y eucalipto.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_17.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_25.webp</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Conquista Definitiva</t>
+          <t>Despertar de Alegría</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>$165.000</t>
+          <t>$95.000</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rosas</t>
+          <t>Gerberas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2892,27 +2892,27 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 24 rosas y claveles con tarjeta personalizada. Para dejar claro lo que sientes.</t>
+          <t>Ramo de 10 gerberas con tarjeta o mensaje personalizado. Color y alegría al instante.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_21.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_18.webp</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Obra Maestra</t>
+          <t>Fusión Perfecta</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>$265.000</t>
+          <t>$227.500</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2932,27 +2932,27 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 60 rosas y claveles con tarjeta personalizada. Abundancia que impresiona.</t>
+          <t>Ramo de 36 rosas y 6 girasoles con tarjeta personalizada. Elegancia y energía en un solo ramo.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_1.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_2.webp</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vitamina Emocional</t>
+          <t>Garantía de Amor</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>$110.000</t>
+          <t>$102.500</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Girasoles</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2972,27 +2972,27 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Ramo de 4 girasoles con tarjeta o mensaje personalizado. Alegría garantizada.</t>
+          <t>Ramo de 12 rosas con tarjeta o mensaje personalizado. El clásico que siempre funciona.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_23.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_17.webp</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Guardián del Corazón</t>
+          <t>Conquista Definitiva</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>$275.000</t>
+          <t>$165.000</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Con Peluche</t>
+          <t>Rosas</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3012,50 +3012,170 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Osito de 25 cm en rosas de foamy dentro de caja de acetato, con tarjeta y 3 globos de helio. Un detalle que perdura.</t>
+          <t>Ramo de 24 rosas y claveles con tarjeta personalizada. Para dejar claro lo que sientes.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_24.webp</t>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_21.webp</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
+        <v>1</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Obra Maestra</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>$265.000</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OCULTO (foto 1–26)</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Rosas</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>No (oculto temporalmente)</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>Ramo de 60 rosas y claveles con tarjeta personalizada. Abundancia que impresiona.</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_1.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>23</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Vitamina Emocional</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>$110.000</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>OCULTO (foto 1–26)</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Girasoles</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>No (oculto temporalmente)</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>Ramo de 4 girasoles con tarjeta o mensaje personalizado. Alegría garantizada.</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_23.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>24</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Guardián del Corazón</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>$275.000</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>OCULTO (foto 1–26)</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Con Peluche</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>No (oculto temporalmente)</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>Osito de 25 cm en rosas de foamy dentro de caja de acetato, con tarjeta y 3 globos de helio. Un detalle que perdura.</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_24.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
         <v>26</v>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B70" t="inlineStr">
         <is>
           <t>Reflejo de Amor</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C70" t="inlineStr">
         <is>
           <t>$212.000</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D70" t="inlineStr">
         <is>
           <t>OCULTO (foto 1–26)</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E70" t="inlineStr">
         <is>
           <t>Rosas</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>No (oculto temporalmente)</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>Arreglo circular de rosas rojas alrededor de un espejo grabado “Eres la mejor mamá”. Elegancia con un mensaje eterno.</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>https://florescucuta.dondeseria.com/assets/flores_cucuta_26.webp</t>
         </is>
